--- a/EKG_Kalite_Yönetim_Sistemi/09_Risk Azaltma ve PFMEA/02_RR2 - Risk Aksiyonları ve Türev Akışlar/EKG-PRJ-LST-07_pfmea_aksiyon_ve_en_yuksek_risk_azaltma_firsatlari_list.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/09_Risk Azaltma ve PFMEA/02_RR2 - Risk Aksiyonları ve Türev Akışlar/EKG-PRJ-LST-07_pfmea_aksiyon_ve_en_yuksek_risk_azaltma_firsatlari_list.xlsx
@@ -751,7 +751,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-LST-07&amp;C&amp;"Arial,Regular"&amp;11PFMEA Aksiyon ve En Yüksek Risk Azaltma Fırsatları Listesi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 23.09.2026
+Revizyon nedeni: Hedef ve gerçekleşen riskler ayrıldı; sayısal AP endeksi kaldırıldı ve risk takibi sadeleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -864,7 +865,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-LST-07&amp;C&amp;"Arial,Regular"&amp;11PFMEA Aksiyon ve En Yüksek Risk Azaltma Fırsatları Listesi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 23.09.2026
+Revizyon nedeni: Hedef ve gerçekleşen riskler ayrıldı; sayısal AP endeksi kaldırıldı ve risk takibi sadeleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>